--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -12994,7 +12994,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -13468,7 +13468,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13778,7 +13778,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -14460,7 +14460,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -14708,7 +14708,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -15328,7 +15328,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -15514,7 +15514,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -15638,7 +15638,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -16010,7 +16010,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -16258,7 +16258,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -16444,7 +16444,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -16506,7 +16506,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16940,7 +16940,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -17064,7 +17064,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -17436,7 +17436,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -17684,7 +17684,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -17932,7 +17932,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17994,7 +17994,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -18366,7 +18366,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -18924,7 +18924,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -19048,7 +19048,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -19172,7 +19172,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -19234,7 +19234,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -19420,7 +19420,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -19792,7 +19792,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19978,7 +19978,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -20412,7 +20412,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -20598,7 +20598,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -21118,7 +21118,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -21444,7 +21444,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -22422,7 +22422,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22748,7 +22748,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -23074,7 +23074,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -23198,7 +23198,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -23524,7 +23524,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -24052,7 +24052,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -24378,7 +24378,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -24704,7 +24704,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -24828,7 +24828,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -25030,7 +25030,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -25154,7 +25154,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -25356,7 +25356,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -25480,7 +25480,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -25806,7 +25806,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -26008,7 +26008,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -26660,7 +26660,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -26784,7 +26784,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -26986,7 +26986,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -27110,7 +27110,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -27312,7 +27312,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -27436,7 +27436,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -27638,7 +27638,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -27964,7 +27964,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -28088,7 +28088,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -28290,7 +28290,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -28616,7 +28616,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -28740,7 +28740,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -28942,7 +28942,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -29392,7 +29392,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -29594,7 +29594,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -29718,7 +29718,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -29920,7 +29920,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -30386,7 +30386,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -30588,7 +30588,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -30720,7 +30720,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -31515,7 +31515,7 @@
           <t>F | 337呎 (1房)
 $955万
 $28,350/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31570,7 @@
           <t>F | 337呎 (1房)
 $942万
 $27,964/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -31625,7 +31625,7 @@
           <t>F | 337呎 (1房)
 $940万
 $27,902/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -31680,7 +31680,7 @@
           <t>F | 337呎 (1房)
 $936万
 $27,786/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -31735,7 +31735,7 @@
           <t>F | 337呎 (1房)
 $934万
 $27,727/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -32285,7 +32285,7 @@
           <t>F | 337呎 (1房)
 $957万
 $28,386/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
     </row>
@@ -32395,7 +32395,7 @@
           <t>F | 337呎 (1房)
 $910万
 $27,000/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -32450,7 +32450,7 @@
           <t>F | 337呎 (1房)
 $919万
 $27,261/呎
-(26年-06月-29日)</t>
+(26年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -32505,7 +32505,7 @@
           <t>F | 337呎 (1房)
 $917万
 $27,208/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -32615,7 +32615,7 @@
           <t>F | 337呎 (1房)
 $913万
 $27,098/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
     </row>
@@ -32670,7 +32670,7 @@
           <t>F | 337呎 (1房)
 $910万
 $26,991/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -32725,7 +32725,7 @@
           <t>F | 337呎 (1房)
 $897万
 $26,623/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -32780,7 +32780,7 @@
           <t>F | 337呎 (1房)
 $894万
 $26,516/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -32835,7 +32835,7 @@
           <t>F | 337呎 (1房)
 $892万
 $26,466/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -32890,7 +32890,7 @@
           <t>F | 337呎 (1房)
 $890万
 $26,412/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -32945,7 +32945,7 @@
           <t>F | 337呎 (1房)
 $888万
 $26,359/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -33000,7 +33000,7 @@
           <t>F | 337呎 (1房)
 $918万
 $27,234/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -33055,7 +33055,7 @@
           <t>F | 300呎 (1房)
 $912万
 $30,400/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
     </row>
@@ -33201,7 +33201,7 @@
           <t>B | 337呎 (1房)
 $949万
 $28,163/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -33209,7 +33209,7 @@
           <t>C | 440呎 (2房)
 $1243万
 $28,252/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -33240,7 +33240,7 @@
           <t>B | 337呎 (1房)
 $992万
 $29,421/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -33248,7 +33248,7 @@
           <t>C | 440呎 (2房)
 $1240万
 $28,191/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -33256,7 +33256,7 @@
           <t>D | 340呎 (1房)
 $956万
 $28,115/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -33279,7 +33279,7 @@
           <t>B | 337呎 (1房)
 $989万
 $29,359/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -33287,7 +33287,7 @@
           <t>C | 440呎 (2房)
 $1296万
 $29,452/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
@@ -33295,7 +33295,7 @@
           <t>D | 340呎 (1房)
 $999万
 $29,371/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -33310,7 +33310,7 @@
           <t>A | 577呎 (2房)
 $1935万
 $33,541/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -33318,7 +33318,7 @@
           <t>B | 337呎 (1房)
 $943万
 $27,982/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -33326,7 +33326,7 @@
           <t>C | 440呎 (2房)
 $1235万
 $28,070/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
@@ -33334,7 +33334,7 @@
           <t>D | 340呎 (1房)
 $996万
 $29,309/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -33349,7 +33349,7 @@
           <t>A | 577呎 (2房)
 $1863万
 $32,295/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -33357,7 +33357,7 @@
           <t>B | 337呎 (1房)
 $941万
 $27,920/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -33365,7 +33365,7 @@
           <t>C | 440呎 (2房)
 $1232万
 $28,011/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -33373,7 +33373,7 @@
           <t>D | 340呎 (1房)
 $950万
 $27,935/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -33396,7 +33396,7 @@
           <t>B | 337呎 (1房)
 $954万
 $28,294/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -33404,7 +33404,7 @@
           <t>C | 440呎 (2房)
 $1227万
 $27,895/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -33412,7 +33412,7 @@
           <t>D | 340呎 (1房)
 $946万
 $27,818/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -33427,7 +33427,7 @@
           <t>A | 577呎 (2房)
 $1846万
 $31,991/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -33435,7 +33435,7 @@
           <t>B | 337呎 (1房)
 $935万
 $27,745/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -33443,7 +33443,7 @@
           <t>C | 440呎 (2房)
 $1225万
 $27,834/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -33451,7 +33451,7 @@
           <t>D | 340呎 (1房)
 $941万
 $27,676/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -33466,7 +33466,7 @@
           <t>A | 577呎 (2房)
 $1840万
 $31,891/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -33474,7 +33474,7 @@
           <t>B | 337呎 (1房)
 $933万
 $27,688/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -33482,7 +33482,7 @@
           <t>C | 440呎 (2房)
 $1222万
 $27,777/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -33490,7 +33490,7 @@
           <t>D | 340呎 (1房)
 $939万
 $27,618/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -33505,7 +33505,7 @@
           <t>A | 577呎 (2房)
 $1834万
 $31,790/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -33513,7 +33513,7 @@
           <t>B | 337呎 (1房)
 $975万
 $28,932/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -33521,7 +33521,7 @@
           <t>C | 440呎 (2房)
 $1277万
 $29,023/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -33529,7 +33529,7 @@
           <t>D | 340呎 (1房)
 $937万
 $27,559/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -33544,7 +33544,7 @@
           <t>A | 577呎 (2房)
 $1829万
 $31,692/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -33552,7 +33552,7 @@
           <t>B | 337呎 (1房)
 $929万
 $27,573/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -33560,7 +33560,7 @@
           <t>C | 440呎 (2房)
 $1260万
 $28,636/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -33568,7 +33568,7 @@
           <t>D | 340呎 (1房)
 $979万
 $28,794/呎
-(26年-06月-15日)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -33583,7 +33583,7 @@
           <t>A | 577呎 (2房)
 $1844万
 $31,964/呎
-(26年-06月-28日)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -33591,7 +33591,7 @@
           <t>B | 337呎 (1房)
 $927万
 $27,513/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -33599,7 +33599,7 @@
           <t>C | 440呎 (2房)
 $1272万
 $28,902/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -33630,7 +33630,7 @@
           <t>B | 337呎 (1房)
 $925万
 $27,457/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -33638,7 +33638,7 @@
           <t>C | 440呎 (2房)
 $1212万
 $27,545/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -33669,7 +33669,7 @@
           <t>B | 337呎 (1房)
 $923万
 $27,398/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -33677,7 +33677,7 @@
           <t>C | 440呎 (2房)
 $1209万
 $27,486/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -33700,7 +33700,7 @@
           <t>A | 577呎 (2房)
 $1869万
 $32,399/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -33708,7 +33708,7 @@
           <t>B | 337呎 (1房)
 $921万
 $27,341/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -33716,7 +33716,7 @@
           <t>C | 440呎 (2房)
 $1250万
 $28,398/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -33739,7 +33739,7 @@
           <t>A | 577呎 (2房)
 $1795万
 $31,107/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -33747,7 +33747,7 @@
           <t>B | 337呎 (1房)
 $934万
 $27,715/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -33755,7 +33755,7 @@
           <t>C | 440呎 (2房)
 $1202万
 $27,320/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -33778,7 +33778,7 @@
           <t>A | 577呎 (2房)
 $1874万
 $32,475/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -33786,7 +33786,7 @@
           <t>B | 337呎 (1房)
 $948万
 $28,136/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -33794,7 +33794,7 @@
           <t>C | 440呎 (2房)
 $1200万
 $27,266/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -33802,7 +33802,7 @@
           <t>D | 340呎 (1房)
 $965万
 $28,385/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -33817,7 +33817,7 @@
           <t>A | 577呎 (2房)
 $1784万
 $30,922/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -33825,7 +33825,7 @@
           <t>B | 337呎 (1房)
 $957万
 $28,401/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -33833,7 +33833,7 @@
           <t>C | 440呎 (2房)
 $1197万
 $27,211/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -33856,7 +33856,7 @@
           <t>A | 577呎 (2房)
 $1779万
 $30,830/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -33864,7 +33864,7 @@
           <t>B | 337呎 (1房)
 $955万
 $28,344/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -33872,7 +33872,7 @@
           <t>C | 440呎 (2房)
 $1195万
 $27,157/呎
-(26年-03月-21日)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -33895,7 +33895,7 @@
           <t>A | 577呎 (2房)
 $1774万
 $30,738/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -33903,7 +33903,7 @@
           <t>B | 337呎 (1房)
 $953万
 $28,288/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -33911,7 +33911,7 @@
           <t>C | 440呎 (2房)
 $1192万
 $27,102/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -33934,7 +33934,7 @@
           <t>A | 577呎 (2房)
 $1831万
 $31,728/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -33942,7 +33942,7 @@
           <t>B | 337呎 (1房)
 $909万
 $26,961/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -33950,7 +33950,7 @@
           <t>C | 440呎 (2房)
 $1190万
 $27,048/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -33973,7 +33973,7 @@
           <t>A | 577呎 (2房)
 $1846万
 $31,991/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -33981,7 +33981,7 @@
           <t>B | 337呎 (1房)
 $907万
 $26,908/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -33989,7 +33989,7 @@
           <t>C | 440呎 (2房)
 $1244万
 $28,264/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -33997,7 +33997,7 @@
           <t>D | 340呎 (1房)
 $954万
 $28,047/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -34012,7 +34012,7 @@
           <t>A | 577呎 (2房)
 $1758万
 $30,463/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -34020,7 +34020,7 @@
           <t>B | 337呎 (1房)
 $952万
 $28,255/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -34028,7 +34028,7 @@
           <t>C | 440呎 (2房)
 $1247万
 $28,345/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -34051,7 +34051,7 @@
           <t>A | 577呎 (2房)
 $1752万
 $30,371/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -34059,7 +34059,7 @@
           <t>B | 337呎 (1房)
 $908万
 $26,932/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -34067,7 +34067,7 @@
           <t>C | 440呎 (2房)
 $1189万
 $27,018/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -34090,7 +34090,7 @@
           <t>A | 577呎 (2房)
 $1742万
 $30,191/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -34098,7 +34098,7 @@
           <t>B | 337呎 (1房)
 $904万
 $26,822/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -34106,7 +34106,7 @@
           <t>C | 440呎 (2房)
 $1226万
 $27,859/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -34129,7 +34129,7 @@
           <t>A | 577呎 (2房)
 $1767万
 $30,631/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
@@ -34137,7 +34137,7 @@
           <t>B | 337呎 (1房)
 $918万
 $27,243/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -34145,7 +34145,7 @@
           <t>C | 440呎 (2房)
 $1182万
 $26,855/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -34168,7 +34168,7 @@
           <t>A | 577呎 (2房)
 $1732万
 $30,010/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C30" s="23" t="inlineStr">
@@ -34176,7 +34176,7 @@
           <t>B | 337呎 (1房)
 $904万
 $26,822/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -34184,7 +34184,7 @@
           <t>C | 440呎 (2房)
 $1218万
 $27,693/呎
-(26年-03月-27日)</t>
+(26年-03月-28日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -34207,7 +34207,7 @@
           <t>A | 577呎 (2房)
 $1721万
 $29,830/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
@@ -34215,7 +34215,7 @@
           <t>B | 337呎 (1房)
 $897万
 $26,611/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
@@ -34223,7 +34223,7 @@
           <t>C | 440呎 (2房)
 $1230万
 $27,952/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -34254,7 +34254,7 @@
           <t>B | 337呎 (1房)
 $895万
 $26,555/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
@@ -34262,7 +34262,7 @@
           <t>C | 440呎 (2房)
 $1172万
 $26,643/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -34293,7 +34293,7 @@
           <t>B | 337呎 (1房)
 $893万
 $26,501/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
@@ -34301,7 +34301,7 @@
           <t>C | 440呎 (2房)
 $1225万
 $27,841/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -34324,7 +34324,7 @@
           <t>A | 577呎 (2房)
 $1706万
 $29,563/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="C34" s="23" t="inlineStr">
@@ -34332,7 +34332,7 @@
           <t>B | 337呎 (1房)
 $933万
 $27,694/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -34340,7 +34340,7 @@
           <t>C | 440呎 (2房)
 $1168万
 $26,536/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
@@ -34348,7 +34348,7 @@
           <t>D | 340呎 (1房)
 $901万
 $26,494/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -34379,7 +34379,7 @@
           <t>C | 401呎 (2房)
 $1250万
 $31,172/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -34563,7 +34563,7 @@
           <t>E | 399呎 (2房)
 $1145万
 $28,702/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
     </row>
@@ -34602,7 +34602,7 @@
           <t>D | 342呎 (1房)
 $989万
 $28,906/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -34610,7 +34610,7 @@
           <t>E | 399呎 (2房)
 $1183万
 $29,647/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -34657,7 +34657,7 @@
           <t>E | 399呎 (2房)
 $1140万
 $28,576/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -34704,7 +34704,7 @@
           <t>E | 399呎 (2房)
 $1138万
 $28,516/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -34743,7 +34743,7 @@
           <t>D | 342呎 (1房)
 $965万
 $28,225/呎
-(26年-07月-21日)</t>
+(26年-07月-22日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -34751,7 +34751,7 @@
           <t>E | 399呎 (2房)
 $1135万
 $28,456/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -34798,7 +34798,7 @@
           <t>E | 399呎 (2房)
 $1170万
 $29,336/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -34829,7 +34829,7 @@
           <t>C | 563呎 (2房)
 $1833万
 $32,556/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -34845,7 +34845,7 @@
           <t>E | 399呎 (2房)
 $1125万
 $28,193/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -34876,7 +34876,7 @@
           <t>C | 563呎 (2房)
 $1796万
 $31,892/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -34884,7 +34884,7 @@
           <t>D | 342呎 (1房)
 $960万
 $28,070/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F12" s="23" t="inlineStr">
@@ -34892,7 +34892,7 @@
           <t>E | 399呎 (2房)
 $1123万
 $28,135/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -34939,7 +34939,7 @@
           <t>E | 399呎 (2房)
 $1120万
 $28,075/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -34970,7 +34970,7 @@
           <t>C | 563呎 (2房)
 $1800万
 $31,977/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -34986,7 +34986,7 @@
           <t>E | 399呎 (2房)
 $1157万
 $29,003/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -35033,7 +35033,7 @@
           <t>E | 399呎 (2房)
 $1116万
 $27,957/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
     </row>
@@ -35064,7 +35064,7 @@
           <t>C | 563呎 (2房)
 $1789万
 $31,778/呎
-(26年-07月-13日)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -35080,7 +35080,7 @@
           <t>E | 399呎 (2房)
 $1152万
 $28,882/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -35111,7 +35111,7 @@
           <t>C | 563呎 (2房)
 $1768万
 $31,394/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -35127,7 +35127,7 @@
           <t>E | 399呎 (2房)
 $1111万
 $27,840/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -35158,7 +35158,7 @@
           <t>C | 563呎 (2房)
 $1845万
 $32,767/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -35174,7 +35174,7 @@
           <t>E | 399呎 (2房)
 $1161万
 $29,088/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -35205,7 +35205,7 @@
           <t>C | 563呎 (2房)
 $1767万
 $31,389/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -35221,7 +35221,7 @@
           <t>E | 399呎 (2房)
 $1156万
 $28,972/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -35268,7 +35268,7 @@
           <t>E | 399呎 (2房)
 $1154万
 $28,917/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -35315,7 +35315,7 @@
           <t>E | 399呎 (2房)
 $1100万
 $27,561/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -35346,7 +35346,7 @@
           <t>C | 563呎 (2房)
 $1736万
 $30,829/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -35362,7 +35362,7 @@
           <t>E | 399呎 (2房)
 $1098万
 $27,506/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
     </row>
@@ -35393,7 +35393,7 @@
           <t>C | 563呎 (2房)
 $1731万
 $30,739/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -35409,7 +35409,7 @@
           <t>E | 399呎 (2房)
 $1093万
 $27,396/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -35440,7 +35440,7 @@
           <t>C | 563呎 (2房)
 $1725万
 $30,647/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -35456,7 +35456,7 @@
           <t>E | 399呎 (2房)
 $1091万
 $27,341/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -35487,7 +35487,7 @@
           <t>C | 563呎 (2房)
 $1736万
 $30,829/呎
-(26年-06月-09日)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -35503,7 +35503,7 @@
           <t>E | 399呎 (2房)
 $1089万
 $27,286/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -35534,7 +35534,7 @@
           <t>C | 563呎 (2房)
 $1731万
 $30,739/呎
-(26年-06月-14日)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -35550,7 +35550,7 @@
           <t>E | 399呎 (2房)
 $1087万
 $27,233/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -35581,7 +35581,7 @@
           <t>C | 563呎 (2房)
 $1790万
 $31,801/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -35597,7 +35597,7 @@
           <t>E | 399呎 (2房)
 $1084万
 $27,178/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -35628,7 +35628,7 @@
           <t>C | 563呎 (2房)
 $1700万
 $30,190/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -35644,7 +35644,7 @@
           <t>E | 399呎 (2房)
 $1080万
 $27,070/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -35675,7 +35675,7 @@
           <t>C | 563呎 (2房)
 $1695万
 $30,099/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -35691,7 +35691,7 @@
           <t>E | 399呎 (2房)
 $1129万
 $28,288/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
     </row>
@@ -35722,7 +35722,7 @@
           <t>C | 563呎 (2房)
 $1705万
 $30,282/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -35738,7 +35738,7 @@
           <t>E | 399呎 (2房)
 $1076万
 $26,962/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -35769,7 +35769,7 @@
           <t>C | 563呎 (2房)
 $1680万
 $29,831/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -35785,7 +35785,7 @@
           <t>E | 399呎 (2房)
 $1074万
 $26,907/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -35816,7 +35816,7 @@
           <t>C | 563呎 (2房)
 $1674万
 $29,742/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -35832,7 +35832,7 @@
           <t>E | 399呎 (2房)
 $1078万
 $27,013/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -35863,7 +35863,7 @@
           <t>C | 563呎 (2房)
 $1669万
 $29,652/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -35879,7 +35879,7 @@
           <t>E | 399呎 (2房)
 $1107万
 $27,747/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -35910,7 +35910,7 @@
           <t>C | 563呎 (2房)
 $1679万
 $29,829/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -35926,7 +35926,7 @@
           <t>E | 399呎 (2房)
 $1067万
 $26,747/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -35965,7 +35965,7 @@
           <t>D | 304呎 (1房)
 $1021万
 $33,599/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -12994,7 +12994,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -33055,7 +33055,7 @@
           <t>F | 300呎 (1房)
 $912万
 $30,400/呎
-(26年-07月-20日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -33778,7 +33778,7 @@
           <t>A | 577呎 (2房)
 $1874万
 $32,475/呎
-(26年-07月-18日)</t>
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -35965,7 +35965,7 @@
           <t>D | 304呎 (1房)
 $1021万
 $33,599/呎
-(26年-07月-10日)</t>
+(26年-08月-10日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -16625,34 +16625,34 @@
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
-        <v>10908000</v>
+        <v>9381000</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>32082</v>
+        <v>27591</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K239" s="5" t="n">
-        <v>9380880</v>
+        <v>9381000</v>
       </c>
       <c r="L239" s="5" t="n">
         <v>27591</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N239" s="3" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>96</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -33719,12 +33719,12 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
-$1091万
-$32,082/呎
-(在售)</t>
+$938万
+$27,591/呎
+(26年-08月-13日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -15881,34 +15881,34 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
-        <v>10977000</v>
+        <v>9770000</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>32285</v>
+        <v>28735</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K227" s="5" t="n">
-        <v>9440220</v>
+        <v>9770000</v>
       </c>
       <c r="L227" s="5" t="n">
-        <v>27765</v>
+        <v>28735</v>
       </c>
       <c r="M227" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N227" s="3" t="inlineStr">
@@ -33131,7 +33131,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -33602,12 +33602,12 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 340呎 (1房)
-$1098万
-$32,285/呎
-(在售)</t>
+$977万
+$28,735/呎
+(26年-08月-24日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -785,14 +785,14 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>9595880</v>
+        <v>9707460</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>28474</v>
+        <v>28806</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -1057,14 +1057,14 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>9573520</v>
+        <v>9684840</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>28408</v>
+        <v>28738</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -3529,14 +3529,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>9434200</v>
+        <v>9543900</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>27995</v>
+        <v>28320</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3941,14 +3941,14 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>9413560</v>
+        <v>9523020</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>27933</v>
+        <v>28258</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -4353,14 +4353,14 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>9394640</v>
+        <v>9503880</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>27877</v>
+        <v>28201</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4765,14 +4765,14 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>9374860</v>
+        <v>9483870</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>27819</v>
+        <v>28142</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -5177,14 +5177,14 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>9355080</v>
+        <v>9463860</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>27760</v>
+        <v>28083</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -5589,14 +5589,14 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>9335300</v>
+        <v>9443850</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>27701</v>
+        <v>28023</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -6001,14 +6001,14 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>9315520</v>
+        <v>9423840</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>27642</v>
+        <v>27964</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -6413,14 +6413,14 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
-        <v>9279400</v>
+        <v>9387300</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>27535</v>
+        <v>27855</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6825,14 +6825,14 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>9260480</v>
+        <v>9368160</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>27479</v>
+        <v>27799</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -7649,14 +7649,14 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>9223500</v>
+        <v>9330750</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>27369</v>
+        <v>27688</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -9297,14 +9297,14 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K127" s="5" t="n">
-        <v>9149540</v>
+        <v>9255930</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>27150</v>
+        <v>27466</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -13417,14 +13417,14 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K187" s="5" t="n">
-        <v>9691340</v>
+        <v>9804030</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>28504</v>
+        <v>28835</v>
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
@@ -13603,14 +13603,14 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>19097160</v>
+        <v>19319220</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>33097</v>
+        <v>33482</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -13851,14 +13851,14 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K194" s="5" t="n">
-        <v>19034380</v>
+        <v>19255710</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>32989</v>
+        <v>33372</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -14099,14 +14099,14 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>18971600</v>
+        <v>19192200</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>32880</v>
+        <v>33262</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -14843,14 +14843,14 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K210" s="5" t="n">
-        <v>18734240</v>
+        <v>18952080</v>
       </c>
       <c r="L210" s="5" t="n">
-        <v>32468</v>
+        <v>32846</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
@@ -16145,14 +16145,14 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K231" s="5" t="n">
-        <v>9420440</v>
+        <v>9529980</v>
       </c>
       <c r="L231" s="5" t="n">
-        <v>27707</v>
+        <v>28029</v>
       </c>
       <c r="M231" s="3" t="inlineStr">
         <is>
@@ -16331,14 +16331,14 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K234" s="5" t="n">
-        <v>18384220</v>
+        <v>18597990</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>31862</v>
+        <v>32232</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -16393,14 +16393,14 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
-        <v>9400660</v>
+        <v>9509970</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>27649</v>
+        <v>27970</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
@@ -16579,14 +16579,14 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K238" s="5" t="n">
-        <v>18326600</v>
+        <v>18539700</v>
       </c>
       <c r="L238" s="5" t="n">
-        <v>31762</v>
+        <v>32131</v>
       </c>
       <c r="M238" s="3" t="inlineStr">
         <is>
@@ -16889,14 +16889,14 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K243" s="5" t="n">
-        <v>9343900</v>
+        <v>9452550</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>27482</v>
+        <v>27802</v>
       </c>
       <c r="M243" s="3" t="inlineStr">
         <is>
@@ -17385,14 +17385,14 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K251" s="5" t="n">
-        <v>9306920</v>
+        <v>9415140</v>
       </c>
       <c r="L251" s="5" t="n">
-        <v>27373</v>
+        <v>27692</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -17633,14 +17633,14 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K255" s="5" t="n">
-        <v>9288000</v>
+        <v>9396000</v>
       </c>
       <c r="L255" s="5" t="n">
-        <v>27318</v>
+        <v>27635</v>
       </c>
       <c r="M255" s="3" t="inlineStr">
         <is>
@@ -17881,14 +17881,14 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K259" s="5" t="n">
-        <v>9251020</v>
+        <v>9358590</v>
       </c>
       <c r="L259" s="5" t="n">
-        <v>27209</v>
+        <v>27525</v>
       </c>
       <c r="M259" s="3" t="inlineStr">
         <is>
@@ -18129,14 +18129,14 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K263" s="5" t="n">
-        <v>9232960</v>
+        <v>9340320</v>
       </c>
       <c r="L263" s="5" t="n">
-        <v>27156</v>
+        <v>27472</v>
       </c>
       <c r="M263" s="3" t="inlineStr">
         <is>
@@ -18625,14 +18625,14 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K271" s="5" t="n">
-        <v>9171500</v>
+        <v>9279400</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>26975</v>
+        <v>27292</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
@@ -18873,14 +18873,14 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K275" s="5" t="n">
-        <v>9152800</v>
+        <v>9260480</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>26920</v>
+        <v>27237</v>
       </c>
       <c r="M275" s="3" t="inlineStr">
         <is>
@@ -19121,14 +19121,14 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K279" s="5" t="n">
-        <v>9116250</v>
+        <v>9223500</v>
       </c>
       <c r="L279" s="5" t="n">
-        <v>26812</v>
+        <v>27128</v>
       </c>
       <c r="M279" s="3" t="inlineStr">
         <is>
@@ -19369,14 +19369,14 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K283" s="5" t="n">
-        <v>9098400</v>
+        <v>9205440</v>
       </c>
       <c r="L283" s="5" t="n">
-        <v>26760</v>
+        <v>27075</v>
       </c>
       <c r="M283" s="3" t="inlineStr">
         <is>
@@ -19617,14 +19617,14 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K287" s="5" t="n">
-        <v>9079700</v>
+        <v>9186520</v>
       </c>
       <c r="L287" s="5" t="n">
-        <v>26705</v>
+        <v>27019</v>
       </c>
       <c r="M287" s="3" t="inlineStr">
         <is>
@@ -19865,14 +19865,14 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K291" s="5" t="n">
-        <v>9061850</v>
+        <v>9168460</v>
       </c>
       <c r="L291" s="5" t="n">
-        <v>26652</v>
+        <v>26966</v>
       </c>
       <c r="M291" s="3" t="inlineStr">
         <is>
@@ -20113,14 +20113,14 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>9044000</v>
+        <v>9150400</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>26600</v>
+        <v>26913</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
@@ -20299,14 +20299,14 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K298" s="5" t="n">
-        <v>17362540</v>
+        <v>17564430</v>
       </c>
       <c r="L298" s="5" t="n">
-        <v>30091</v>
+        <v>30441</v>
       </c>
       <c r="M298" s="3" t="inlineStr">
         <is>
@@ -20361,14 +20361,14 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K299" s="5" t="n">
-        <v>9025300</v>
+        <v>9131480</v>
       </c>
       <c r="L299" s="5" t="n">
-        <v>26545</v>
+        <v>26857</v>
       </c>
       <c r="M299" s="3" t="inlineStr">
         <is>
@@ -20547,14 +20547,14 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K302" s="5" t="n">
-        <v>17310080</v>
+        <v>17511360</v>
       </c>
       <c r="L302" s="5" t="n">
-        <v>30000</v>
+        <v>30349</v>
       </c>
       <c r="M302" s="3" t="inlineStr">
         <is>
@@ -21191,14 +21191,14 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K312" s="5" t="n">
-        <v>9734200</v>
+        <v>9848720</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>28463</v>
+        <v>28797</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
@@ -21253,14 +21253,14 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K313" s="5" t="n">
-        <v>18582700</v>
+        <v>18801320</v>
       </c>
       <c r="L313" s="5" t="n">
-        <v>33007</v>
+        <v>33395</v>
       </c>
       <c r="M313" s="3" t="inlineStr">
         <is>
@@ -21579,14 +21579,14 @@
       </c>
       <c r="J318" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K318" s="5" t="n">
-        <v>18522350</v>
+        <v>18740260</v>
       </c>
       <c r="L318" s="5" t="n">
-        <v>32899</v>
+        <v>33286</v>
       </c>
       <c r="M318" s="3" t="inlineStr">
         <is>
@@ -21843,14 +21843,14 @@
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K322" s="5" t="n">
-        <v>9692550</v>
+        <v>9806580</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>28341</v>
+        <v>28674</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
@@ -21905,14 +21905,14 @@
       </c>
       <c r="J323" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K323" s="5" t="n">
-        <v>18511500</v>
+        <v>18726750</v>
       </c>
       <c r="L323" s="5" t="n">
-        <v>32880</v>
+        <v>33262</v>
       </c>
       <c r="M323" s="3" t="inlineStr">
         <is>
@@ -22169,14 +22169,14 @@
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K327" s="5" t="n">
-        <v>9672150</v>
+        <v>9785940</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>28281</v>
+        <v>28614</v>
       </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
@@ -22231,14 +22231,14 @@
       </c>
       <c r="J328" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="K328" s="5" t="n">
-        <v>18453020</v>
+        <v>18667590</v>
       </c>
       <c r="L328" s="5" t="n">
-        <v>32776</v>
+        <v>33157</v>
       </c>
       <c r="M328" s="3" t="inlineStr">
         <is>
@@ -22557,14 +22557,14 @@
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K333" s="5" t="n">
-        <v>18345550</v>
+        <v>18561380</v>
       </c>
       <c r="L333" s="5" t="n">
-        <v>32585</v>
+        <v>32969</v>
       </c>
       <c r="M333" s="3" t="inlineStr">
         <is>
@@ -22821,14 +22821,14 @@
       </c>
       <c r="J337" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K337" s="5" t="n">
-        <v>9611800</v>
+        <v>9724880</v>
       </c>
       <c r="L337" s="5" t="n">
-        <v>28105</v>
+        <v>28435</v>
       </c>
       <c r="M337" s="3" t="inlineStr">
         <is>
@@ -22883,14 +22883,14 @@
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K338" s="5" t="n">
-        <v>18230800</v>
+        <v>18445280</v>
       </c>
       <c r="L338" s="5" t="n">
-        <v>32382</v>
+        <v>32762</v>
       </c>
       <c r="M338" s="3" t="inlineStr">
         <is>
@@ -23147,14 +23147,14 @@
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>9562500</v>
+        <v>9675000</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>27961</v>
+        <v>28289</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
@@ -23799,14 +23799,14 @@
       </c>
       <c r="J352" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K352" s="5" t="n">
-        <v>9522550</v>
+        <v>9634580</v>
       </c>
       <c r="L352" s="5" t="n">
-        <v>27844</v>
+        <v>28171</v>
       </c>
       <c r="M352" s="3" t="inlineStr">
         <is>
@@ -23861,14 +23861,14 @@
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K353" s="5" t="n">
-        <v>18059100</v>
+        <v>18271560</v>
       </c>
       <c r="L353" s="5" t="n">
-        <v>32077</v>
+        <v>32454</v>
       </c>
       <c r="M353" s="3" t="inlineStr">
         <is>
@@ -24125,14 +24125,14 @@
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K357" s="5" t="n">
-        <v>9503000</v>
+        <v>9614800</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>27787</v>
+        <v>28113</v>
       </c>
       <c r="M357" s="3" t="inlineStr">
         <is>
@@ -24451,14 +24451,14 @@
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K362" s="5" t="n">
-        <v>9482600</v>
+        <v>9594160</v>
       </c>
       <c r="L362" s="5" t="n">
-        <v>27727</v>
+        <v>28053</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
@@ -24513,14 +24513,14 @@
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K363" s="5" t="n">
-        <v>17946050</v>
+        <v>18157180</v>
       </c>
       <c r="L363" s="5" t="n">
-        <v>31876</v>
+        <v>32251</v>
       </c>
       <c r="M363" s="3" t="inlineStr">
         <is>
@@ -24777,14 +24777,14 @@
       </c>
       <c r="J367" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K367" s="5" t="n">
-        <v>9463050</v>
+        <v>9574380</v>
       </c>
       <c r="L367" s="5" t="n">
-        <v>27670</v>
+        <v>27995</v>
       </c>
       <c r="M367" s="3" t="inlineStr">
         <is>
@@ -25103,14 +25103,14 @@
       </c>
       <c r="J372" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K372" s="5" t="n">
-        <v>9443500</v>
+        <v>9554600</v>
       </c>
       <c r="L372" s="5" t="n">
-        <v>27613</v>
+        <v>27937</v>
       </c>
       <c r="M372" s="3" t="inlineStr">
         <is>
@@ -25429,14 +25429,14 @@
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K377" s="5" t="n">
-        <v>9423100</v>
+        <v>9533960</v>
       </c>
       <c r="L377" s="5" t="n">
-        <v>27553</v>
+        <v>27877</v>
       </c>
       <c r="M377" s="3" t="inlineStr">
         <is>
@@ -25755,14 +25755,14 @@
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K382" s="5" t="n">
-        <v>9385700</v>
+        <v>9496120</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>27444</v>
+        <v>27766</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -26081,14 +26081,14 @@
       </c>
       <c r="J387" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K387" s="5" t="n">
-        <v>9366150</v>
+        <v>9476340</v>
       </c>
       <c r="L387" s="5" t="n">
-        <v>27386</v>
+        <v>27709</v>
       </c>
       <c r="M387" s="3" t="inlineStr">
         <is>
@@ -26143,14 +26143,14 @@
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K388" s="5" t="n">
-        <v>17618800</v>
+        <v>17826080</v>
       </c>
       <c r="L388" s="5" t="n">
-        <v>31294</v>
+        <v>31663</v>
       </c>
       <c r="M388" s="3" t="inlineStr">
         <is>
@@ -26407,14 +26407,14 @@
       </c>
       <c r="J392" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K392" s="5" t="n">
-        <v>9348300</v>
+        <v>9458280</v>
       </c>
       <c r="L392" s="5" t="n">
-        <v>27334</v>
+        <v>27656</v>
       </c>
       <c r="M392" s="3" t="inlineStr">
         <is>
@@ -26469,14 +26469,14 @@
       </c>
       <c r="J393" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K393" s="5" t="n">
-        <v>17565250</v>
+        <v>17771900</v>
       </c>
       <c r="L393" s="5" t="n">
-        <v>31199</v>
+        <v>31566</v>
       </c>
       <c r="M393" s="3" t="inlineStr">
         <is>
@@ -26733,14 +26733,14 @@
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K397" s="5" t="n">
-        <v>9330450</v>
+        <v>9440220</v>
       </c>
       <c r="L397" s="5" t="n">
-        <v>27282</v>
+        <v>27603</v>
       </c>
       <c r="M397" s="3" t="inlineStr">
         <is>
@@ -27059,14 +27059,14 @@
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K402" s="5" t="n">
-        <v>9291350</v>
+        <v>9400660</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>27168</v>
+        <v>27487</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
@@ -27385,14 +27385,14 @@
       </c>
       <c r="J407" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K407" s="5" t="n">
-        <v>9274350</v>
+        <v>9383460</v>
       </c>
       <c r="L407" s="5" t="n">
-        <v>27118</v>
+        <v>27437</v>
       </c>
       <c r="M407" s="3" t="inlineStr">
         <is>
@@ -27711,14 +27711,14 @@
       </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K412" s="5" t="n">
-        <v>9255650</v>
+        <v>9364540</v>
       </c>
       <c r="L412" s="5" t="n">
-        <v>27063</v>
+        <v>27382</v>
       </c>
       <c r="M412" s="3" t="inlineStr">
         <is>
@@ -28037,14 +28037,14 @@
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K417" s="5" t="n">
-        <v>9237800</v>
+        <v>9346480</v>
       </c>
       <c r="L417" s="5" t="n">
-        <v>27011</v>
+        <v>27329</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
@@ -28363,14 +28363,14 @@
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K422" s="5" t="n">
-        <v>9218250</v>
+        <v>9326700</v>
       </c>
       <c r="L422" s="5" t="n">
-        <v>26954</v>
+        <v>27271</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
@@ -28689,14 +28689,14 @@
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K427" s="5" t="n">
-        <v>9181700</v>
+        <v>9289720</v>
       </c>
       <c r="L427" s="5" t="n">
-        <v>26847</v>
+        <v>27163</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
@@ -29015,14 +29015,14 @@
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K432" s="5" t="n">
-        <v>9163850</v>
+        <v>9271660</v>
       </c>
       <c r="L432" s="5" t="n">
-        <v>26795</v>
+        <v>27110</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
@@ -29341,14 +29341,14 @@
       </c>
       <c r="J437" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K437" s="5" t="n">
-        <v>9146000</v>
+        <v>9253600</v>
       </c>
       <c r="L437" s="5" t="n">
-        <v>26743</v>
+        <v>27057</v>
       </c>
       <c r="M437" s="3" t="inlineStr">
         <is>
@@ -29667,14 +29667,14 @@
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="K442" s="5" t="n">
-        <v>9126450</v>
+        <v>9233820</v>
       </c>
       <c r="L442" s="5" t="n">
-        <v>26686</v>
+        <v>26999</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -5161,34 +5161,34 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
-        <v>10878000</v>
+        <v>9356000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>32279</v>
+        <v>27763</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>9463860</v>
+        <v>9356000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>28083</v>
+        <v>27763</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
@@ -5573,34 +5573,34 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>10855000</v>
+        <v>9336000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>32211</v>
+        <v>27703</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>9443850</v>
+        <v>9336000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>28023</v>
+        <v>27703</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
@@ -31307,7 +31307,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31317,7 +31317,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -32005,12 +32005,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
-$1088万
-$32,279/呎
-(在售)</t>
+$936万
+$27,763/呎
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -32060,12 +32060,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
-$1086万
-$32,211/呎
-(在售)</t>
+$934万
+$27,703/呎
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
+++ b/web/files/港岛-香港仔及鸭脷洲-Deep Water South 第6A期.xlsx
@@ -4337,34 +4337,34 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>10924000</v>
+        <v>9395000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>32415</v>
+        <v>27878</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>9503880</v>
+        <v>9395000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>28201</v>
+        <v>27878</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -13835,34 +13835,34 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
-        <v>22133000</v>
+        <v>19035000</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>38359</v>
+        <v>32990</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K194" s="5" t="n">
-        <v>19255710</v>
+        <v>19035000</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>33372</v>
+        <v>32990</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>90 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N194" s="3" t="inlineStr">
@@ -16630,7 +16630,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -31307,7 +31307,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -31317,7 +31317,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -31895,12 +31895,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 337呎 (1房)
-$1092万
-$32,415/呎
-(在售)</t>
+$940万
+$27,878/呎
+(26年-08月-31日)</t>
         </is>
       </c>
     </row>
@@ -33131,7 +33131,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -33227,12 +33227,12 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 577呎 (2房)
-$2213万
-$38,359/呎
-(在售)</t>
+$1904万
+$32,990/呎
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
@@ -33724,7 +33724,7 @@
           <t>D | 340呎 (1房)
 $938万
 $27,591/呎
-(26年-08月-13日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
     </row>
